--- a/resources/templates/standard/A4200-01.xlsx
+++ b/resources/templates/standard/A4200-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>보존기록 목록표</t>
   </si>
@@ -585,12 +588,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.65" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -625,7 +630,7 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
@@ -676,7 +681,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
@@ -727,7 +732,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
@@ -790,11 +795,11 @@
     </row>
     <row r="5" ht="18.65" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -805,7 +810,7 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
@@ -818,7 +823,7 @@
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
@@ -832,7 +837,7 @@
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
       <c r="AI5" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ5" s="11"/>
       <c r="AK5" s="11"/>
@@ -840,13 +845,13 @@
       <c r="AM5" s="11"/>
       <c r="AN5" s="11"/>
       <c r="AO5" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP5" s="12"/>
       <c r="AQ5" s="12"/>
       <c r="AR5" s="12"/>
       <c r="AS5" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT5" s="11"/>
       <c r="AU5" s="11"/>
@@ -855,17 +860,17 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -881,30 +886,30 @@
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="13"/>
       <c r="AC6" s="13"/>
       <c r="AD6" s="13"/>
       <c r="AE6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF6" s="13"/>
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
       <c r="AI6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ6" s="13"/>
       <c r="AK6" s="13"/>
       <c r="AL6" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM6" s="13"/>
       <c r="AN6" s="13"/>
